--- a/inst/extdata/wb_projects_gov_menaap.xlsx
+++ b/inst/extdata/wb_projects_gov_menaap.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -52,6 +52,18 @@
   </si>
   <si>
     <t xml:space="preserve">commitment_amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theme_pfm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theme_procurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theme_public_admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theme_env_social</t>
   </si>
   <si>
     <t xml:space="preserve">comments</t>
@@ -545,7 +557,11 @@
     <col min="11" max="11" width="32.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="14.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="17.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="8.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="16.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -591,135 +607,183 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2021</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>304000000</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>25</v>
+      <c r="N2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>2021</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>400000000</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>25</v>
+      <c r="N3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2026</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M4" s="1"/>
-      <c r="N4" s="1" t="s">
-        <v>25</v>
+      <c r="N4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -746,7 +810,11 @@
     <col min="11" max="11" width="32.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="14.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="17.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="8.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="16.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -792,193 +860,265 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
-        <v>25</v>
+      <c r="N2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>2018</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="1" t="s">
-        <v>25</v>
+      <c r="N3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2018</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1" t="s">
-        <v>25</v>
+      <c r="N4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2027</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="1" t="s">
-        <v>25</v>
+      <c r="N5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2027</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="1" t="s">
-        <v>25</v>
+      <c r="N6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/wb_projects_gov_menaap.xlsx
+++ b/inst/extdata/wb_projects_gov_menaap.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -33,6 +33,12 @@
     <t xml:space="preserve">proj_approval_fy</t>
   </si>
   <si>
+    <t xml:space="preserve">asa_cn_approval_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">task_type</t>
+  </si>
+  <si>
     <t xml:space="preserve">proj_url</t>
   </si>
   <si>
@@ -190,6 +196,9 @@
   </si>
   <si>
     <t xml:space="preserve">Republic of Yemen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advisory</t>
   </si>
   <si>
     <t xml:space="preserve">https://opswork.worldbank.org/home/P506552</t>
@@ -214,7 +223,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -249,8 +260,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -550,240 +562,254 @@
     <col min="4" max="4" width="52.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="28.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="42.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="18.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="7.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="32.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="14.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="17.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="20.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="17.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="7.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="32.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="16.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="9.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>304000000</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="P2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="1" t="n">
+      <c r="Q2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" s="1" t="n">
+      <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>29</v>
+      <c r="T2" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>400000000</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="1" t="n">
+      <c r="O4" s="2"/>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>29</v>
+      <c r="R4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -803,322 +829,346 @@
     <col min="4" max="4" width="52.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="28.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="42.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="40.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="18.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="7.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="32.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="14.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="17.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="20.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="40.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="7.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="32.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="16.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="9.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="B2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>2015</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1" t="n">
+      <c r="J2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>29</v>
+      <c r="Q2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>29</v>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>29</v>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="B5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>2027</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>29</v>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1" t="n">
+      <c r="I6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>29</v>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/wb_projects_gov_menaap.xlsx
+++ b/inst/extdata/wb_projects_gov_menaap.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -72,6 +72,9 @@
     <t xml:space="preserve">theme_env_social</t>
   </si>
   <si>
+    <t xml:space="preserve">ida_cycle_approval</t>
+  </si>
+  <si>
     <t xml:space="preserve">comments</t>
   </si>
   <si>
@@ -108,6 +111,9 @@
     <t xml:space="preserve">IBRD</t>
   </si>
   <si>
+    <t xml:space="preserve">Pre-IDA21</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
@@ -145,6 +151,9 @@
   </si>
   <si>
     <t xml:space="preserve">Winston Percy Onipede Cole (ADM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDA21</t>
   </si>
   <si>
     <t xml:space="preserve">P154282</t>
@@ -575,7 +584,8 @@
     <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
     <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
     <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="8.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="18.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -639,22 +649,25 @@
       <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>2021</v>
@@ -662,22 +675,22 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>304000000</v>
@@ -695,24 +708,27 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>2021</v>
@@ -720,22 +736,22 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>400000000</v>
@@ -753,24 +769,27 @@
         <v>1</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>2026</v>
@@ -778,22 +797,22 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="n">
@@ -809,7 +828,10 @@
         <v>0</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -842,7 +864,8 @@
     <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
     <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
     <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="8.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="18.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -906,22 +929,25 @@
       <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>2015</v>
@@ -929,17 +955,17 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -956,24 +982,27 @@
         <v>0</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>2018</v>
@@ -981,17 +1010,17 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1008,24 +1037,27 @@
         <v>0</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>2018</v>
@@ -1033,17 +1065,17 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1060,42 +1092,47 @@
         <v>0</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>2027</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" s="2" t="n">
+        <v>45643</v>
+      </c>
       <c r="H5" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1112,24 +1149,27 @@
         <v>0</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>2027</v>
@@ -1138,20 +1178,20 @@
         <v>45880</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1168,7 +1208,10 @@
         <v>0</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/wb_projects_gov_menaap.xlsx
+++ b/inst/extdata/wb_projects_gov_menaap.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -33,7 +33,7 @@
     <t xml:space="preserve">proj_approval_fy</t>
   </si>
   <si>
-    <t xml:space="preserve">asa_cn_approval_date</t>
+    <t xml:space="preserve">asa_approval_date</t>
   </si>
   <si>
     <t xml:space="preserve">task_type</t>
@@ -156,61 +156,22 @@
     <t xml:space="preserve">IDA21</t>
   </si>
   <si>
-    <t xml:space="preserve">P154282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKGRW Implementation Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faced by an adverse security situation and weak fundamentals, Pakistan?s economy is struggling to slowly recover from a low-investment low-growth trap. The Government of Pakistan has recognized the urgency of the economic situation and has embarked on a major structural reform program.  The Government?s Economic Reform Program (ERP) includes a set of bold stabilization and structural reform measures aimed at reducing the risk of a balance of payment crisis in the short term and regain and sustain high and inclusive growth in the medium term. While the Government?s ERP has shown early gains in stabilizing the economy and implementing initial actions into structural reforms, there are substantial downside risks to the program, including gaps in knowledge, weak capacity of the government to complete the design and implement the program, and difficulty gaining wide buy-in.  The Trust Fund?s main development objective is to support the government?s economic reform program by filling knowledge gaps, strengthening the capacity of key institutions?federal and provincial--to complete the design and implement the reform agenda, and building dialogue and consensus. More specifically, it will provide assistance for key federal and provincial ministries and agencies, to expand and sustain the fiscal space and revenue collection; liberalize trade and economic activities; facilitate private investment; improve the quality of expenditures and debt management and tackle other binding constraints facing the economy.     The TF will be initially established with a main component including four implementing reform windows (also called child trust funds), grouped around the four key reform priorities of the Government: (i) Energy sector reforms, (ii) State-owned enterprises and private sector reforms, (iii) Tax reforms, and (iv) Public debt management reforms.  Other windows may also be established through which priority reforms could be financed that do not fall neatly within the other four windows.  The task for which this AIS has been prepared relates to administration of the trust fund for which the Bank is responsible through the MDTF Secretariat.  Administering the trust fund will require maintaining records, arranging meetings, preparing application check-lists, assisting in preparing financial and progress reports, providing procurement and disbursement guidance to PMTs, engaging in effective communication and external relations, and assisting PMTs in the organization of capacity building activities.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P154282</t>
+    <t xml:space="preserve">P506552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yemen Strengthening Institutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Republic of Yemen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advisory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opswork.worldbank.org/home/P506552</t>
   </si>
   <si>
     <t xml:space="preserve">Analytic and Advisory Activities Product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keiko Nagai (ADM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P158097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strengthening Sub-National Tax Adm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobilize domestic tax resources through tax policy and tax administration reforms, in order to increase the fiscal space of Pakistan with a view to funding quality social expenditure and improving the provision of public services.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P158097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raul Felix Junquera-Varela (ADM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P158095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modernization of Revenue Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P158095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P506552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yemen Strengthening Institutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Republic of Yemen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advisory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P506552</t>
   </si>
   <si>
     <t xml:space="preserve">Saki Kumagai (ADM)</t>
@@ -571,7 +532,7 @@
     <col min="4" max="4" width="52.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="28.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="20.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="17.71" hidden="0" customWidth="1"/>
@@ -849,9 +810,9 @@
     <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="52.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="28.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="20.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="40.71" hidden="0" customWidth="1"/>
@@ -940,37 +901,39 @@
       <c r="B2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2015</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+        <v>2027</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>45643</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="I2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>0</v>
@@ -982,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>33</v>
@@ -990,42 +953,46 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+        <v>2027</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="I3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
         <v>29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
@@ -1037,180 +1004,9 @@
         <v>0</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>45643</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>45880</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="U6" s="2" t="s">
         <v>33</v>
       </c>
     </row>

--- a/inst/extdata/wb_projects_gov_menaap.xlsx
+++ b/inst/extdata/wb_projects_gov_menaap.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -156,6 +156,48 @@
     <t xml:space="preserve">IDA21</t>
   </si>
   <si>
+    <t xml:space="preserve">P154282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKGRW Implementation Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faced by an adverse security situation and weak fundamentals, Pakistan?s economy is struggling to slowly recover from a low-investment low-growth trap. The Government of Pakistan has recognized the urgency of the economic situation and has embarked on a major structural reform program.  The Government?s Economic Reform Program (ERP) includes a set of bold stabilization and structural reform measures aimed at reducing the risk of a balance of payment crisis in the short term and regain and sustain high and inclusive growth in the medium term. While the Government?s ERP has shown early gains in stabilizing the economy and implementing initial actions into structural reforms, there are substantial downside risks to the program, including gaps in knowledge, weak capacity of the government to complete the design and implement the program, and difficulty gaining wide buy-in.  The Trust Fund?s main development objective is to support the government?s economic reform program by filling knowledge gaps, strengthening the capacity of key institutions?federal and provincial--to complete the design and implement the reform agenda, and building dialogue and consensus. More specifically, it will provide assistance for key federal and provincial ministries and agencies, to expand and sustain the fiscal space and revenue collection; liberalize trade and economic activities; facilitate private investment; improve the quality of expenditures and debt management and tackle other binding constraints facing the economy.     The TF will be initially established with a main component including four implementing reform windows (also called child trust funds), grouped around the four key reform priorities of the Government: (i) Energy sector reforms, (ii) State-owned enterprises and private sector reforms, (iii) Tax reforms, and (iv) Public debt management reforms.  Other windows may also be established through which priority reforms could be financed that do not fall neatly within the other four windows.  The task for which this AIS has been prepared relates to administration of the trust fund for which the Bank is responsible through the MDTF Secretariat.  Administering the trust fund will require maintaining records, arranging meetings, preparing application check-lists, assisting in preparing financial and progress reports, providing procurement and disbursement guidance to PMTs, engaging in effective communication and external relations, and assisting PMTs in the organization of capacity building activities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opswork.worldbank.org/home/P154282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytic and Advisory Activities Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keiko Nagai (ADM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P158097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strengthening Sub-National Tax Adm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobilize domestic tax resources through tax policy and tax administration reforms, in order to increase the fiscal space of Pakistan with a view to funding quality social expenditure and improving the provision of public services.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opswork.worldbank.org/home/P158097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raul Felix Junquera-Varela (ADM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P158095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modernization of Revenue Administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opswork.worldbank.org/home/P158095</t>
+  </si>
+  <si>
     <t xml:space="preserve">P506552</t>
   </si>
   <si>
@@ -169,9 +211,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://opswork.worldbank.org/home/P506552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analytic and Advisory Activities Product</t>
   </si>
   <si>
     <t xml:space="preserve">Saki Kumagai (ADM)</t>
@@ -810,7 +849,7 @@
     <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="52.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="28.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
@@ -901,39 +940,35 @@
       <c r="B2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>45643</v>
-      </c>
-      <c r="H2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>0</v>
@@ -944,69 +979,226 @@
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="T2" s="2"/>
       <c r="U2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>45880</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>50</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
         <v>29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>45643</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="2" t="s">
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="U6" s="2" t="s">
         <v>33</v>
       </c>
     </row>

--- a/inst/extdata/wb_projects_gov_menaap.xlsx
+++ b/inst/extdata/wb_projects_gov_menaap.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -156,61 +156,22 @@
     <t xml:space="preserve">IDA21</t>
   </si>
   <si>
-    <t xml:space="preserve">P154282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKGRW Implementation Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faced by an adverse security situation and weak fundamentals, Pakistan?s economy is struggling to slowly recover from a low-investment low-growth trap. The Government of Pakistan has recognized the urgency of the economic situation and has embarked on a major structural reform program.  The Government?s Economic Reform Program (ERP) includes a set of bold stabilization and structural reform measures aimed at reducing the risk of a balance of payment crisis in the short term and regain and sustain high and inclusive growth in the medium term. While the Government?s ERP has shown early gains in stabilizing the economy and implementing initial actions into structural reforms, there are substantial downside risks to the program, including gaps in knowledge, weak capacity of the government to complete the design and implement the program, and difficulty gaining wide buy-in.  The Trust Fund?s main development objective is to support the government?s economic reform program by filling knowledge gaps, strengthening the capacity of key institutions?federal and provincial--to complete the design and implement the reform agenda, and building dialogue and consensus. More specifically, it will provide assistance for key federal and provincial ministries and agencies, to expand and sustain the fiscal space and revenue collection; liberalize trade and economic activities; facilitate private investment; improve the quality of expenditures and debt management and tackle other binding constraints facing the economy.     The TF will be initially established with a main component including four implementing reform windows (also called child trust funds), grouped around the four key reform priorities of the Government: (i) Energy sector reforms, (ii) State-owned enterprises and private sector reforms, (iii) Tax reforms, and (iv) Public debt management reforms.  Other windows may also be established through which priority reforms could be financed that do not fall neatly within the other four windows.  The task for which this AIS has been prepared relates to administration of the trust fund for which the Bank is responsible through the MDTF Secretariat.  Administering the trust fund will require maintaining records, arranging meetings, preparing application check-lists, assisting in preparing financial and progress reports, providing procurement and disbursement guidance to PMTs, engaging in effective communication and external relations, and assisting PMTs in the organization of capacity building activities.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P154282</t>
+    <t xml:space="preserve">P506552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yemen Strengthening Institutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Republic of Yemen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advisory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opswork.worldbank.org/home/P506552</t>
   </si>
   <si>
     <t xml:space="preserve">Analytic and Advisory Activities Product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keiko Nagai (ADM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P158097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strengthening Sub-National Tax Adm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobilize domestic tax resources through tax policy and tax administration reforms, in order to increase the fiscal space of Pakistan with a view to funding quality social expenditure and improving the provision of public services.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P158097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raul Felix Junquera-Varela (ADM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P158095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modernization of Revenue Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P158095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P506552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yemen Strengthening Institutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Republic of Yemen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advisory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P506552</t>
   </si>
   <si>
     <t xml:space="preserve">Saki Kumagai (ADM)</t>
@@ -849,7 +810,7 @@
     <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="52.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="28.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
@@ -940,35 +901,39 @@
       <c r="B2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>45643</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="I2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>0</v>
@@ -979,47 +944,55 @@
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="2"/>
+      <c r="T2" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="U2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="I3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
         <v>29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
@@ -1030,175 +1003,10 @@
       <c r="S3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="2"/>
+      <c r="T3" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="U3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>45643</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>45880</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="U6" s="2" t="s">
         <v>33</v>
       </c>
     </row>

--- a/inst/extdata/wb_projects_gov_menaap.xlsx
+++ b/inst/extdata/wb_projects_gov_menaap.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -27,6 +27,9 @@
     <t xml:space="preserve">region</t>
   </si>
   <si>
+    <t xml:space="preserve">country_code</t>
+  </si>
+  <si>
     <t xml:space="preserve">country_name</t>
   </si>
   <si>
@@ -90,6 +93,9 @@
     <t xml:space="preserve">Middle East, North Africa, Afghanistan, and Pakistan</t>
   </si>
   <si>
+    <t xml:space="preserve">PAK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Islamic Republic of Pakistan</t>
   </si>
   <si>
@@ -141,6 +147,9 @@
     <t xml:space="preserve">The project development objective (PDO) is to establish public financial management reform coordination capacity, strengthen budget controls and improve transparency in the use of public funds.</t>
   </si>
   <si>
+    <t xml:space="preserve">SYR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Syrian Arab Republic</t>
   </si>
   <si>
@@ -160,6 +169,9 @@
   </si>
   <si>
     <t xml:space="preserve">Yemen Strengthening Institutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YEM</t>
   </si>
   <si>
     <t xml:space="preserve">Republic of Yemen</t>
@@ -530,23 +542,24 @@
     <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="52.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="28.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="17.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="7.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="32.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="9.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="18.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="28.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="9.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="42.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="17.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="18.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="7.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="32.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="14.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="17.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="9.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="17.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="18.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="16.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="18.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -613,186 +626,198 @@
       <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" s="2" t="n">
         <v>304000000</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>32</v>
+      <c r="T2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="2" t="n">
         <v>400000000</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>32</v>
+      <c r="T3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P4" s="2"/>
       <c r="Q4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R4" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>46</v>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -810,23 +835,24 @@
     <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="52.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="40.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="7.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="32.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="9.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="18.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="20.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="9.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="42.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="40.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="18.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="7.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="32.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="14.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="17.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="9.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="17.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="18.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="16.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="18.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -893,48 +919,51 @@
       <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>45643</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="2"/>
       <c r="M2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="N2" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="O2" s="2"/>
-      <c r="P2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P2" s="2"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
@@ -944,70 +973,76 @@
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>32</v>
+      <c r="T2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="J3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>45880</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="L3" s="2"/>
       <c r="M3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N3" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="O3" s="2"/>
-      <c r="P3" s="2" t="n">
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>46</v>
+      <c r="T3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
